--- a/backend/implant_library_v4.xlsx
+++ b/backend/implant_library_v4.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/abhijit/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/abhijit/Documents/College /Apps/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C834964E-79B8-E143-AF3C-99D7395BE7E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95546A0D-5288-484A-AD33-BDC38B3DA433}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="80" yWindow="580" windowWidth="25520" windowHeight="14620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,15 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="880" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="974" uniqueCount="70">
   <si>
     <t>Diameter_mm</t>
   </si>
   <si>
     <t>Length_mm</t>
-  </si>
-  <si>
-    <t>Cowellmedi INNO Submerged Narrow</t>
   </si>
   <si>
     <t>Noble Biocare</t>
@@ -184,9 +181,6 @@
     <t xml:space="preserve">Alpha Bio </t>
   </si>
   <si>
-    <t>Bio SPI</t>
-  </si>
-  <si>
     <t>Blue Sky Bio</t>
   </si>
   <si>
@@ -218,6 +212,24 @@
   </si>
   <si>
     <t>Implant System</t>
+  </si>
+  <si>
+    <t>SPI</t>
+  </si>
+  <si>
+    <t>BSPI</t>
+  </si>
+  <si>
+    <t>Tapered Pro Conical RBT</t>
+  </si>
+  <si>
+    <t>Progressive Line</t>
+  </si>
+  <si>
+    <t>Conelog</t>
+  </si>
+  <si>
+    <t>Tapered Short Conical RBT</t>
   </si>
 </sst>
 </file>
@@ -594,7 +606,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D439"/>
+  <dimension ref="A1:D486"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.6640625" customWidth="1"/>
@@ -605,10 +617,10 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
@@ -619,10 +631,10 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C2">
         <v>3</v>
@@ -633,10 +645,10 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C3">
         <v>3</v>
@@ -647,10 +659,10 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -661,10 +673,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C5">
         <v>3</v>
@@ -675,10 +687,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C6">
         <v>3.5</v>
@@ -689,10 +701,10 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C7">
         <v>3.5</v>
@@ -703,10 +715,10 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C8">
         <v>3.5</v>
@@ -717,10 +729,10 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C9">
         <v>3.5</v>
@@ -731,10 +743,10 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C10">
         <v>3.5</v>
@@ -745,10 +757,10 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11">
         <v>3.5</v>
@@ -759,10 +771,10 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C12">
         <v>4.3</v>
@@ -773,10 +785,10 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C13">
         <v>4.3</v>
@@ -787,10 +799,10 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B14" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C14">
         <v>4.3</v>
@@ -801,10 +813,10 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B15" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C15">
         <v>4.3</v>
@@ -815,10 +827,10 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C16">
         <v>4.3</v>
@@ -829,10 +841,10 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B17" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C17">
         <v>4.3</v>
@@ -843,10 +855,10 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B18" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18">
         <v>5</v>
@@ -857,10 +869,10 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C19">
         <v>5</v>
@@ -871,10 +883,10 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B20" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C20">
         <v>5</v>
@@ -885,10 +897,10 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B21" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C21">
         <v>5</v>
@@ -899,10 +911,10 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B22" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C22">
         <v>5</v>
@@ -913,10 +925,10 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B23" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C23">
         <v>5</v>
@@ -927,10 +939,10 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B24" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C24">
         <v>5.5</v>
@@ -941,10 +953,10 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B25" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C25">
         <v>5.5</v>
@@ -955,10 +967,10 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B26" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C26">
         <v>5.5</v>
@@ -969,10 +981,10 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B27" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C27">
         <v>5.5</v>
@@ -983,10 +995,10 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B28" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C28">
         <v>5.5</v>
@@ -997,10 +1009,10 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B29" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C29">
         <v>5.5</v>
@@ -1011,10 +1023,10 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B30" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C30">
         <v>3.75</v>
@@ -1025,10 +1037,10 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B31" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C31">
         <v>3.75</v>
@@ -1039,10 +1051,10 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B32" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C32">
         <v>3.75</v>
@@ -1053,10 +1065,10 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B33" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C33">
         <v>3.75</v>
@@ -1067,10 +1079,10 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B34" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C34">
         <v>3.75</v>
@@ -1081,10 +1093,10 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B35" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C35">
         <v>3.75</v>
@@ -1095,10 +1107,10 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B36" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C36">
         <v>3.75</v>
@@ -1109,10 +1121,10 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B37" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C37">
         <v>4.3</v>
@@ -1123,10 +1135,10 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B38" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C38">
         <v>4.3</v>
@@ -1137,10 +1149,10 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B39" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C39">
         <v>4.3</v>
@@ -1151,10 +1163,10 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B40" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C40">
         <v>4.3</v>
@@ -1165,10 +1177,10 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B41" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C41">
         <v>4.3</v>
@@ -1179,10 +1191,10 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B42" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C42">
         <v>4.3</v>
@@ -1193,10 +1205,10 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B43" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C43">
         <v>4.3</v>
@@ -1207,10 +1219,10 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B44" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C44">
         <v>5</v>
@@ -1221,10 +1233,10 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B45" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C45">
         <v>5</v>
@@ -1235,10 +1247,10 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B46" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C46">
         <v>5</v>
@@ -1249,10 +1261,10 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B47" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C47">
         <v>5</v>
@@ -1263,10 +1275,10 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B48" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C48">
         <v>5</v>
@@ -1277,10 +1289,10 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B49" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C49">
         <v>5</v>
@@ -1291,10 +1303,10 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B50" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C50">
         <v>5</v>
@@ -1305,10 +1317,10 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
+        <v>2</v>
+      </c>
+      <c r="B51" t="s">
         <v>3</v>
-      </c>
-      <c r="B51" t="s">
-        <v>4</v>
       </c>
       <c r="C51">
         <v>5.5</v>
@@ -1319,10 +1331,10 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
+        <v>2</v>
+      </c>
+      <c r="B52" t="s">
         <v>3</v>
-      </c>
-      <c r="B52" t="s">
-        <v>4</v>
       </c>
       <c r="C52">
         <v>5.5</v>
@@ -1333,10 +1345,10 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
+        <v>2</v>
+      </c>
+      <c r="B53" t="s">
         <v>3</v>
-      </c>
-      <c r="B53" t="s">
-        <v>4</v>
       </c>
       <c r="C53">
         <v>5.5</v>
@@ -1347,10 +1359,10 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
+        <v>2</v>
+      </c>
+      <c r="B54" t="s">
         <v>3</v>
-      </c>
-      <c r="B54" t="s">
-        <v>4</v>
       </c>
       <c r="C54">
         <v>5.5</v>
@@ -1361,10 +1373,10 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
+        <v>2</v>
+      </c>
+      <c r="B55" t="s">
         <v>3</v>
-      </c>
-      <c r="B55" t="s">
-        <v>4</v>
       </c>
       <c r="C55">
         <v>5.5</v>
@@ -1375,10 +1387,10 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
+        <v>2</v>
+      </c>
+      <c r="B56" t="s">
         <v>3</v>
-      </c>
-      <c r="B56" t="s">
-        <v>4</v>
       </c>
       <c r="C56">
         <v>5.5</v>
@@ -1389,10 +1401,10 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B57" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C57">
         <v>3.3</v>
@@ -1403,10 +1415,10 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
+        <v>11</v>
+      </c>
+      <c r="B58" t="s">
         <v>12</v>
-      </c>
-      <c r="B58" t="s">
-        <v>13</v>
       </c>
       <c r="C58">
         <v>4.0999999999999996</v>
@@ -1417,10 +1429,10 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
+        <v>11</v>
+      </c>
+      <c r="B59" t="s">
         <v>12</v>
-      </c>
-      <c r="B59" t="s">
-        <v>13</v>
       </c>
       <c r="C59">
         <v>4.8</v>
@@ -1431,10 +1443,10 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
+        <v>11</v>
+      </c>
+      <c r="B60" t="s">
         <v>12</v>
-      </c>
-      <c r="B60" t="s">
-        <v>13</v>
       </c>
       <c r="C60">
         <v>6.5</v>
@@ -1445,10 +1457,10 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
+        <v>13</v>
+      </c>
+      <c r="B61" t="s">
         <v>14</v>
-      </c>
-      <c r="B61" t="s">
-        <v>15</v>
       </c>
       <c r="C61">
         <v>3.5</v>
@@ -1459,10 +1471,10 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
+        <v>13</v>
+      </c>
+      <c r="B62" t="s">
         <v>14</v>
-      </c>
-      <c r="B62" t="s">
-        <v>15</v>
       </c>
       <c r="C62">
         <v>3.75</v>
@@ -1473,10 +1485,10 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
+        <v>13</v>
+      </c>
+      <c r="B63" t="s">
         <v>14</v>
-      </c>
-      <c r="B63" t="s">
-        <v>15</v>
       </c>
       <c r="C63">
         <v>4</v>
@@ -1487,10 +1499,10 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
+        <v>13</v>
+      </c>
+      <c r="B64" t="s">
         <v>14</v>
-      </c>
-      <c r="B64" t="s">
-        <v>15</v>
       </c>
       <c r="C64">
         <v>4</v>
@@ -1501,10 +1513,10 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
+        <v>13</v>
+      </c>
+      <c r="B65" t="s">
         <v>14</v>
-      </c>
-      <c r="B65" t="s">
-        <v>15</v>
       </c>
       <c r="C65">
         <v>5</v>
@@ -1515,10 +1527,10 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
+        <v>13</v>
+      </c>
+      <c r="B66" t="s">
         <v>14</v>
-      </c>
-      <c r="B66" t="s">
-        <v>15</v>
       </c>
       <c r="C66">
         <v>6</v>
@@ -1529,10 +1541,10 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B67" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C67" s="2">
         <v>3.5</v>
@@ -1543,10 +1555,10 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B68" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C68" s="2">
         <v>3.75</v>
@@ -1557,10 +1569,10 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B69" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C69" s="2">
         <v>4</v>
@@ -1571,10 +1583,10 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B70" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C70" s="2">
         <v>4</v>
@@ -1585,10 +1597,10 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A71" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B71" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C71" s="2">
         <v>5</v>
@@ -1599,10 +1611,10 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A72" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B72" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C72" s="2">
         <v>6</v>
@@ -1613,10 +1625,10 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A73" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B73" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C73" s="2">
         <v>3.5</v>
@@ -1627,10 +1639,10 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A74" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B74" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C74" s="2">
         <v>3.5</v>
@@ -1641,10 +1653,10 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A75" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B75" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C75" s="2">
         <v>4.3</v>
@@ -1655,10 +1667,10 @@
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A76" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B76" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C76" s="2">
         <v>4.3</v>
@@ -1669,10 +1681,10 @@
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A77" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B77" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C77" s="2">
         <v>5</v>
@@ -1683,10 +1695,10 @@
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A78" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B78" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C78" s="2">
         <v>5</v>
@@ -1697,10 +1709,10 @@
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A79" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B79" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C79" s="2">
         <v>3.5</v>
@@ -1711,10 +1723,10 @@
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A80" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B80" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C80" s="2">
         <v>3.5</v>
@@ -1725,10 +1737,10 @@
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A81" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B81" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C81" s="2">
         <v>4.3</v>
@@ -1739,10 +1751,10 @@
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A82" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B82" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C82" s="2">
         <v>4.3</v>
@@ -1753,10 +1765,10 @@
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A83" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B83" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C83" s="2">
         <v>5</v>
@@ -1767,10 +1779,10 @@
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A84" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B84" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C84" s="2">
         <v>5</v>
@@ -1781,10 +1793,10 @@
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A85" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B85" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C85" s="2">
         <v>3.5</v>
@@ -1795,10 +1807,10 @@
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A86" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B86" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C86" s="2">
         <v>3.5</v>
@@ -1809,10 +1821,10 @@
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A87" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B87" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C87" s="2">
         <v>3.75</v>
@@ -1823,10 +1835,10 @@
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A88" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B88" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C88" s="2">
         <v>3.75</v>
@@ -1837,10 +1849,10 @@
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A89" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B89" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C89" s="2">
         <v>4</v>
@@ -1851,10 +1863,10 @@
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A90" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B90" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C90" s="2">
         <v>4</v>
@@ -1865,10 +1877,10 @@
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A91" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B91" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C91" s="2">
         <v>5</v>
@@ -1879,10 +1891,10 @@
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A92" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B92" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C92" s="2">
         <v>3.5</v>
@@ -1893,10 +1905,10 @@
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A93" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B93" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C93" s="2">
         <v>3.5</v>
@@ -1907,10 +1919,10 @@
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A94" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B94" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C94" s="2">
         <v>3.75</v>
@@ -1921,10 +1933,10 @@
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A95" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B95" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C95" s="2">
         <v>3.75</v>
@@ -1935,10 +1947,10 @@
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A96" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B96" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C96" s="2">
         <v>4</v>
@@ -1949,10 +1961,10 @@
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A97" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B97" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C97" s="2">
         <v>4</v>
@@ -1963,10 +1975,10 @@
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A98" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B98" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C98" s="2">
         <v>5</v>
@@ -1977,10 +1989,10 @@
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B99" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C99">
         <v>3.5</v>
@@ -1991,10 +2003,10 @@
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
+        <v>21</v>
+      </c>
+      <c r="B100" t="s">
         <v>22</v>
-      </c>
-      <c r="B100" t="s">
-        <v>23</v>
       </c>
       <c r="C100">
         <v>4</v>
@@ -2005,10 +2017,10 @@
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
+        <v>21</v>
+      </c>
+      <c r="B101" t="s">
         <v>22</v>
-      </c>
-      <c r="B101" t="s">
-        <v>23</v>
       </c>
       <c r="C101">
         <v>4.5</v>
@@ -2019,10 +2031,10 @@
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B102" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C102">
         <v>5.5</v>
@@ -2033,10 +2045,10 @@
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B103" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C103">
         <v>3.5</v>
@@ -2047,10 +2059,10 @@
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B104" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C104">
         <v>4</v>
@@ -2061,10 +2073,10 @@
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B105" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C105">
         <v>4.5</v>
@@ -2075,10 +2087,10 @@
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B106" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C106">
         <v>3.5</v>
@@ -2089,10 +2101,10 @@
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B107" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C107">
         <v>4</v>
@@ -2103,10 +2115,10 @@
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B108" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C108">
         <v>4.5</v>
@@ -2117,10 +2129,10 @@
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B109" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C109">
         <v>5</v>
@@ -2131,10 +2143,10 @@
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B110" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C110">
         <v>6</v>
@@ -2145,10 +2157,10 @@
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
+        <v>25</v>
+      </c>
+      <c r="B111" t="s">
         <v>26</v>
-      </c>
-      <c r="B111" t="s">
-        <v>27</v>
       </c>
       <c r="C111">
         <v>3.1</v>
@@ -2159,10 +2171,10 @@
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
+        <v>25</v>
+      </c>
+      <c r="B112" t="s">
         <v>26</v>
-      </c>
-      <c r="B112" t="s">
-        <v>27</v>
       </c>
       <c r="C112">
         <v>3.1</v>
@@ -2173,10 +2185,10 @@
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
+        <v>25</v>
+      </c>
+      <c r="B113" t="s">
         <v>26</v>
-      </c>
-      <c r="B113" t="s">
-        <v>27</v>
       </c>
       <c r="C113">
         <v>3.1</v>
@@ -2187,10 +2199,10 @@
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
+        <v>25</v>
+      </c>
+      <c r="B114" t="s">
         <v>26</v>
-      </c>
-      <c r="B114" t="s">
-        <v>2</v>
       </c>
       <c r="C114">
         <v>3.3</v>
@@ -2201,10 +2213,10 @@
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B115" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C115">
         <v>3.5</v>
@@ -2215,10 +2227,10 @@
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B116" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C116">
         <v>4</v>
@@ -2229,10 +2241,10 @@
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B117" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C117">
         <v>4.5</v>
@@ -2243,10 +2255,10 @@
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B118" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C118">
         <v>5</v>
@@ -2257,10 +2269,10 @@
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
+        <v>28</v>
+      </c>
+      <c r="B119" t="s">
         <v>29</v>
-      </c>
-      <c r="B119" t="s">
-        <v>30</v>
       </c>
       <c r="C119">
         <v>4</v>
@@ -2271,10 +2283,10 @@
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
+        <v>28</v>
+      </c>
+      <c r="B120" t="s">
         <v>29</v>
-      </c>
-      <c r="B120" t="s">
-        <v>30</v>
       </c>
       <c r="C120">
         <v>4</v>
@@ -2285,10 +2297,10 @@
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
+        <v>28</v>
+      </c>
+      <c r="B121" t="s">
         <v>29</v>
-      </c>
-      <c r="B121" t="s">
-        <v>30</v>
       </c>
       <c r="C121">
         <v>4.5</v>
@@ -2299,10 +2311,10 @@
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
+        <v>28</v>
+      </c>
+      <c r="B122" t="s">
         <v>29</v>
-      </c>
-      <c r="B122" t="s">
-        <v>30</v>
       </c>
       <c r="C122">
         <v>5</v>
@@ -2313,10 +2325,10 @@
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B123" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C123">
         <v>3.75</v>
@@ -2327,10 +2339,10 @@
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B124" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C124">
         <v>3.75</v>
@@ -2341,10 +2353,10 @@
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B125" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C125">
         <v>4</v>
@@ -2355,10 +2367,10 @@
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B126" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C126">
         <v>4</v>
@@ -2369,10 +2381,10 @@
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B127" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C127">
         <v>5.5</v>
@@ -2383,10 +2395,10 @@
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B128" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C128">
         <v>5.5</v>
@@ -2397,10 +2409,10 @@
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B129" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C129">
         <v>5.5</v>
@@ -2411,10 +2423,10 @@
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B130" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C130">
         <v>6</v>
@@ -2425,10 +2437,10 @@
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B131" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C131">
         <v>6</v>
@@ -2439,10 +2451,10 @@
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B132" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C132">
         <v>3.5</v>
@@ -2453,10 +2465,10 @@
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B133" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C133">
         <v>3.5</v>
@@ -2467,10 +2479,10 @@
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B134" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C134">
         <v>3.5</v>
@@ -2481,10 +2493,10 @@
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B135" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C135">
         <v>3.5</v>
@@ -2495,10 +2507,10 @@
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B136" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C136">
         <v>3.5</v>
@@ -2509,10 +2521,10 @@
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B137" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C137">
         <v>3.5</v>
@@ -2523,10 +2535,10 @@
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A138" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C138" s="2">
         <v>4.5</v>
@@ -2537,10 +2549,10 @@
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A139" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C139" s="2">
         <v>4.5</v>
@@ -2551,10 +2563,10 @@
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A140" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C140" s="2">
         <v>4.5</v>
@@ -2565,10 +2577,10 @@
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A141" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C141" s="2">
         <v>4.5</v>
@@ -2579,10 +2591,10 @@
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A142" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C142" s="2">
         <v>4.5</v>
@@ -2593,10 +2605,10 @@
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A143" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C143" s="2">
         <v>4.5</v>
@@ -2607,10 +2619,10 @@
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A144" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C144" s="2">
         <v>5.5</v>
@@ -2621,10 +2633,10 @@
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A145" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C145" s="2">
         <v>5.5</v>
@@ -2635,10 +2647,10 @@
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A146" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C146" s="2">
         <v>5.5</v>
@@ -2649,10 +2661,10 @@
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A147" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C147" s="2">
         <v>5.5</v>
@@ -2663,10 +2675,10 @@
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A148" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C148" s="2">
         <v>5.5</v>
@@ -2677,10 +2689,10 @@
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A149" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C149" s="2">
         <v>5.5</v>
@@ -2691,10 +2703,10 @@
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A150" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C150" s="2">
         <v>7</v>
@@ -2705,10 +2717,10 @@
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A151" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C151" s="2">
         <v>7</v>
@@ -2719,10 +2731,10 @@
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A152" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C152" s="2">
         <v>7</v>
@@ -2733,10 +2745,10 @@
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A153" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C153" s="2">
         <v>7</v>
@@ -2747,10 +2759,10 @@
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A154" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C154" s="2">
         <v>7</v>
@@ -2761,10 +2773,10 @@
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
+        <v>33</v>
+      </c>
+      <c r="B155" t="s">
         <v>34</v>
-      </c>
-      <c r="B155" t="s">
-        <v>35</v>
       </c>
       <c r="C155">
         <v>3.7</v>
@@ -2775,10 +2787,10 @@
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B156" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C156">
         <v>4.0999999999999996</v>
@@ -2789,10 +2801,10 @@
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B157" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C157">
         <v>4.7</v>
@@ -2803,10 +2815,10 @@
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B158" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C158">
         <v>3.8</v>
@@ -2817,10 +2829,10 @@
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B159" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C159">
         <v>4.2</v>
@@ -2831,10 +2843,10 @@
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B160" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C160">
         <v>4.5999999999999996</v>
@@ -2845,10 +2857,10 @@
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B161" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C161">
         <v>4.5999999999999996</v>
@@ -2859,10 +2871,10 @@
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B162" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C162">
         <v>5.2</v>
@@ -2873,223 +2885,223 @@
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B163" t="s">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="C163">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="D163">
-        <v>10.5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B164" t="s">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="C164">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="D164">
-        <v>12</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B165" t="s">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="C165">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="D165">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B166" t="s">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="C166">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="D166">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B167" t="s">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="C167">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="D167">
-        <v>10.5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B168" t="s">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="C168">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="D168">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B169" t="s">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="C169">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="D169">
-        <v>15</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B170" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="C170">
-        <v>4.5999999999999996</v>
+        <v>3.8</v>
       </c>
       <c r="D170">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B171" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="C171">
-        <v>4.5999999999999996</v>
+        <v>3.8</v>
       </c>
       <c r="D171">
-        <v>7.5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B172" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="C172">
-        <v>5.8</v>
+        <v>3.8</v>
       </c>
       <c r="D172">
-        <v>6</v>
+        <v>18</v>
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B173" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="C173">
-        <v>5.8</v>
+        <v>4.2</v>
       </c>
       <c r="D173">
-        <v>7.5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B174" t="s">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="C174">
-        <v>7</v>
+        <v>4.2</v>
       </c>
       <c r="D174">
-        <v>7.5</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B175" t="s">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="C175">
-        <v>7</v>
+        <v>4.2</v>
       </c>
       <c r="D175">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B176" t="s">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="C176">
-        <v>7</v>
+        <v>4.2</v>
       </c>
       <c r="D176">
-        <v>10.5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B177" t="s">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="C177">
-        <v>8</v>
+        <v>4.2</v>
       </c>
       <c r="D177">
-        <v>7.5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B178" t="s">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="C178">
-        <v>8</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="D178">
         <v>9</v>
@@ -3097,13 +3109,13 @@
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B179" t="s">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="C179">
-        <v>8</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="D179">
         <v>10.5</v>
@@ -3111,1077 +3123,1077 @@
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B180" t="s">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="C180">
-        <v>3.5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="D180">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B181" t="s">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="C181">
-        <v>4</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="D181">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B182" t="s">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="C182">
-        <v>4.5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="D182">
-        <v>11.5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B183" t="s">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="C183">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="D183">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B184" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="C184">
-        <v>3</v>
+        <v>5.2</v>
       </c>
       <c r="D184">
-        <v>8.5</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B185" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="C185">
-        <v>3</v>
+        <v>5.2</v>
       </c>
       <c r="D185">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B186" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="C186">
-        <v>3</v>
+        <v>5.2</v>
       </c>
       <c r="D186">
-        <v>11.5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B187" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="C187">
-        <v>3</v>
+        <v>5.2</v>
       </c>
       <c r="D187">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B188" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="C188">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="D188">
-        <v>15</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B189" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="C189">
-        <v>3.5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="D189">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B190" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="C190">
-        <v>3.5</v>
+        <v>5.2</v>
       </c>
       <c r="D190">
-        <v>10</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B191" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="C191">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="D191">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B192" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="C192">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="D192">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B193" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="C193">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="D193">
         <v>15</v>
       </c>
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A194" s="2" t="s">
-        <v>44</v>
+      <c r="A194" t="s">
+        <v>37</v>
       </c>
       <c r="B194" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="C194">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="D194">
-        <v>8.5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A195" s="2" t="s">
-        <v>44</v>
+      <c r="A195" t="s">
+        <v>37</v>
       </c>
       <c r="B195" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="C195">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="D195">
-        <v>10</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A196" s="2" t="s">
-        <v>44</v>
+      <c r="A196" t="s">
+        <v>37</v>
       </c>
       <c r="B196" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="C196">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="D196">
-        <v>11.5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A197" s="2" t="s">
-        <v>44</v>
+      <c r="A197" t="s">
+        <v>37</v>
       </c>
       <c r="B197" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="C197">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="D197">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A198" s="2" t="s">
-        <v>44</v>
+      <c r="A198" t="s">
+        <v>37</v>
       </c>
       <c r="B198" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C198">
-        <v>4</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="D198">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A199" s="2" t="s">
-        <v>44</v>
+      <c r="A199" t="s">
+        <v>37</v>
       </c>
       <c r="B199" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C199">
-        <v>4.5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="D199">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A200" s="2" t="s">
-        <v>44</v>
+      <c r="A200" t="s">
+        <v>37</v>
       </c>
       <c r="B200" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C200">
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="D200">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A201" s="2" t="s">
-        <v>44</v>
+      <c r="A201" t="s">
+        <v>37</v>
       </c>
       <c r="B201" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C201">
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="D201">
-        <v>11.5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A202" s="2" t="s">
-        <v>44</v>
+      <c r="A202" t="s">
+        <v>37</v>
       </c>
       <c r="B202" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="C202">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="D202">
-        <v>13</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A203" s="2" t="s">
-        <v>44</v>
+      <c r="A203" t="s">
+        <v>37</v>
       </c>
       <c r="B203" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="C203">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="D203">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A204" s="2" t="s">
-        <v>44</v>
+      <c r="A204" t="s">
+        <v>37</v>
       </c>
       <c r="B204" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="C204">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D204">
-        <v>8.5</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A205" s="2" t="s">
-        <v>44</v>
+      <c r="A205" t="s">
+        <v>37</v>
       </c>
       <c r="B205" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="C205">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D205">
-        <v>10</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A206" s="2" t="s">
-        <v>44</v>
+      <c r="A206" t="s">
+        <v>37</v>
       </c>
       <c r="B206" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="C206">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D206">
-        <v>11.5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A207" s="2" t="s">
-        <v>44</v>
+      <c r="A207" t="s">
+        <v>37</v>
       </c>
       <c r="B207" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="C207">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D207">
-        <v>13</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A208" s="2" t="s">
-        <v>44</v>
+      <c r="A208" t="s">
+        <v>68</v>
       </c>
       <c r="B208" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="C208">
-        <v>5</v>
+        <v>3.3</v>
       </c>
       <c r="D208">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A209" s="2" t="s">
-        <v>44</v>
+      <c r="A209" t="s">
+        <v>68</v>
       </c>
       <c r="B209" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="C209">
-        <v>5.5</v>
+        <v>3.3</v>
       </c>
       <c r="D209">
-        <v>8.5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A210" s="2" t="s">
-        <v>44</v>
+      <c r="A210" t="s">
+        <v>68</v>
       </c>
       <c r="B210" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="C210">
-        <v>5.5</v>
+        <v>3.3</v>
       </c>
       <c r="D210">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A211" s="2" t="s">
-        <v>44</v>
+      <c r="A211" t="s">
+        <v>68</v>
       </c>
       <c r="B211" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="C211">
-        <v>5.5</v>
+        <v>3.3</v>
       </c>
       <c r="D211">
-        <v>11.5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A212" s="2" t="s">
-        <v>44</v>
+      <c r="A212" t="s">
+        <v>68</v>
       </c>
       <c r="B212" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="C212">
-        <v>5.5</v>
+        <v>3.8</v>
       </c>
       <c r="D212">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A213" s="2" t="s">
-        <v>44</v>
+      <c r="A213" t="s">
+        <v>68</v>
       </c>
       <c r="B213" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="C213">
-        <v>5.5</v>
+        <v>3.8</v>
       </c>
       <c r="D213">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A214" s="2" t="s">
-        <v>44</v>
+      <c r="A214" t="s">
+        <v>68</v>
       </c>
       <c r="B214" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="C214">
-        <v>6</v>
+        <v>3.8</v>
       </c>
       <c r="D214">
-        <v>8.5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A215" s="2" t="s">
-        <v>44</v>
+      <c r="A215" t="s">
+        <v>68</v>
       </c>
       <c r="B215" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="C215">
-        <v>6</v>
+        <v>3.8</v>
       </c>
       <c r="D215">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A216" s="2" t="s">
-        <v>44</v>
+      <c r="A216" t="s">
+        <v>68</v>
       </c>
       <c r="B216" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="C216">
-        <v>6</v>
+        <v>3.8</v>
       </c>
       <c r="D216">
-        <v>11.5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A217" s="2" t="s">
-        <v>44</v>
+      <c r="A217" t="s">
+        <v>68</v>
       </c>
       <c r="B217" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="C217">
-        <v>6</v>
+        <v>4.3</v>
       </c>
       <c r="D217">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A218" s="2" t="s">
-        <v>44</v>
+      <c r="A218" t="s">
+        <v>68</v>
       </c>
       <c r="B218" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="C218">
-        <v>6</v>
+        <v>4.3</v>
       </c>
       <c r="D218">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A219" s="2" t="s">
-        <v>44</v>
+      <c r="A219" t="s">
+        <v>68</v>
       </c>
       <c r="B219" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="C219">
+        <v>4.3</v>
+      </c>
+      <c r="D219">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A220" t="s">
+        <v>68</v>
+      </c>
+      <c r="B220" t="s">
+        <v>67</v>
+      </c>
+      <c r="C220">
+        <v>4.3</v>
+      </c>
+      <c r="D220">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A221" t="s">
+        <v>68</v>
+      </c>
+      <c r="B221" t="s">
+        <v>67</v>
+      </c>
+      <c r="C221">
+        <v>4.3</v>
+      </c>
+      <c r="D221">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A222" t="s">
+        <v>68</v>
+      </c>
+      <c r="B222" t="s">
+        <v>67</v>
+      </c>
+      <c r="C222">
+        <v>5</v>
+      </c>
+      <c r="D222">
         <v>7</v>
       </c>
-      <c r="D219">
-        <v>8.5</v>
-      </c>
-    </row>
-    <row r="220" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A220" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B220" t="s">
-        <v>49</v>
-      </c>
-      <c r="C220">
+    </row>
+    <row r="223" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A223" t="s">
+        <v>68</v>
+      </c>
+      <c r="B223" t="s">
+        <v>67</v>
+      </c>
+      <c r="C223">
+        <v>5</v>
+      </c>
+      <c r="D223">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A224" t="s">
+        <v>68</v>
+      </c>
+      <c r="B224" t="s">
+        <v>67</v>
+      </c>
+      <c r="C224">
+        <v>5</v>
+      </c>
+      <c r="D224">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A225" t="s">
+        <v>68</v>
+      </c>
+      <c r="B225" t="s">
+        <v>67</v>
+      </c>
+      <c r="C225">
+        <v>5</v>
+      </c>
+      <c r="D225">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A226" t="s">
+        <v>68</v>
+      </c>
+      <c r="B226" t="s">
+        <v>67</v>
+      </c>
+      <c r="C226">
+        <v>5</v>
+      </c>
+      <c r="D226">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A227" t="s">
+        <v>42</v>
+      </c>
+      <c r="B227" t="s">
+        <v>41</v>
+      </c>
+      <c r="C227">
+        <v>3.8</v>
+      </c>
+      <c r="D227">
         <v>7</v>
       </c>
-      <c r="D220">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="221" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A221" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B221" t="s">
-        <v>49</v>
-      </c>
-      <c r="C221">
-        <v>7</v>
-      </c>
-      <c r="D221">
-        <v>11.5</v>
-      </c>
-    </row>
-    <row r="222" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A222" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B222" t="s">
-        <v>49</v>
-      </c>
-      <c r="C222">
-        <v>7</v>
-      </c>
-      <c r="D222">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="223" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A223" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B223" t="s">
-        <v>49</v>
-      </c>
-      <c r="C223">
-        <v>7</v>
-      </c>
-      <c r="D223">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="224" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A224" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B224" t="s">
-        <v>48</v>
-      </c>
-      <c r="C224">
-        <v>4</v>
-      </c>
-      <c r="D224">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="225" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A225" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B225" t="s">
-        <v>48</v>
-      </c>
-      <c r="C225">
-        <v>4</v>
-      </c>
-      <c r="D225">
-        <v>8.5</v>
-      </c>
-    </row>
-    <row r="226" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A226" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B226" t="s">
-        <v>48</v>
-      </c>
-      <c r="C226">
-        <v>4</v>
-      </c>
-      <c r="D226">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="227" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A227" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B227" t="s">
-        <v>48</v>
-      </c>
-      <c r="C227">
-        <v>4</v>
-      </c>
-      <c r="D227">
-        <v>11.5</v>
-      </c>
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A228" s="2" t="s">
-        <v>44</v>
+      <c r="A228" t="s">
+        <v>42</v>
       </c>
       <c r="B228" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="C228">
         <v>4</v>
       </c>
       <c r="D228">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A229" s="2" t="s">
-        <v>44</v>
+      <c r="A229" t="s">
+        <v>42</v>
       </c>
       <c r="B229" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="C229">
         <v>4.5</v>
       </c>
       <c r="D229">
-        <v>7</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A230" s="2" t="s">
-        <v>44</v>
+      <c r="A230" t="s">
+        <v>42</v>
       </c>
       <c r="B230" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="C230">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="D230">
-        <v>8.5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A231" s="2" t="s">
-        <v>44</v>
+      <c r="A231" t="s">
+        <v>43</v>
       </c>
       <c r="B231" t="s">
         <v>48</v>
       </c>
       <c r="C231">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="D231">
-        <v>10</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A232" s="2" t="s">
-        <v>44</v>
+      <c r="A232" t="s">
+        <v>43</v>
       </c>
       <c r="B232" t="s">
         <v>48</v>
       </c>
       <c r="C232">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="D232">
-        <v>11.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A233" s="2" t="s">
-        <v>44</v>
+      <c r="A233" t="s">
+        <v>43</v>
       </c>
       <c r="B233" t="s">
         <v>48</v>
       </c>
       <c r="C233">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="D233">
-        <v>13</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A234" s="2" t="s">
-        <v>44</v>
+      <c r="A234" t="s">
+        <v>43</v>
       </c>
       <c r="B234" t="s">
         <v>48</v>
       </c>
       <c r="C234">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D234">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A235" s="2" t="s">
-        <v>44</v>
+      <c r="A235" t="s">
+        <v>43</v>
       </c>
       <c r="B235" t="s">
         <v>48</v>
       </c>
       <c r="C235">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D235">
-        <v>8.5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A236" s="2" t="s">
-        <v>44</v>
+      <c r="A236" t="s">
+        <v>43</v>
       </c>
       <c r="B236" t="s">
         <v>48</v>
       </c>
       <c r="C236">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="D236">
-        <v>10</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A237" s="2" t="s">
-        <v>44</v>
+      <c r="A237" t="s">
+        <v>43</v>
       </c>
       <c r="B237" t="s">
         <v>48</v>
       </c>
       <c r="C237">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="D237">
-        <v>11.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A238" s="2" t="s">
-        <v>44</v>
+      <c r="A238" t="s">
+        <v>43</v>
       </c>
       <c r="B238" t="s">
         <v>48</v>
       </c>
       <c r="C238">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="D238">
-        <v>13</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A239" s="2" t="s">
-        <v>44</v>
+      <c r="A239" t="s">
+        <v>43</v>
       </c>
       <c r="B239" t="s">
         <v>48</v>
       </c>
       <c r="C239">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="D239">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A240" s="2" t="s">
-        <v>44</v>
+      <c r="A240" t="s">
+        <v>43</v>
       </c>
       <c r="B240" t="s">
         <v>48</v>
       </c>
       <c r="C240">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="D240">
-        <v>8.5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A241" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B241" t="s">
         <v>48</v>
       </c>
       <c r="C241">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D241">
-        <v>10</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A242" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B242" t="s">
         <v>48</v>
       </c>
       <c r="C242">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D242">
-        <v>11.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A243" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B243" t="s">
         <v>48</v>
       </c>
       <c r="C243">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D243">
-        <v>13</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A244" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B244" t="s">
         <v>48</v>
       </c>
       <c r="C244">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D244">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A245" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B245" t="s">
         <v>48</v>
       </c>
       <c r="C245">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D245">
-        <v>8.5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A246" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B246" t="s">
         <v>48</v>
       </c>
       <c r="C246">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="D246">
-        <v>10</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A247" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B247" t="s">
         <v>48</v>
       </c>
       <c r="C247">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="D247">
-        <v>11.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A248" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B248" t="s">
         <v>48</v>
       </c>
       <c r="C248">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="D248">
-        <v>13</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A249" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B249" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C249">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D249">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A250" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B250" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C250">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D250">
-        <v>8.5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A251" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B251" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C251">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="D251">
-        <v>10</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A252" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B252" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C252">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="D252">
-        <v>11.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A253" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B253" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C253">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="D253">
-        <v>13</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A254" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B254" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C254">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="D254">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A255" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B255" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C255">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D255">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A256" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B256" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C256">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="D256">
         <v>8.5</v>
@@ -4189,13 +4201,13 @@
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A257" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B257" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C257">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="D257">
         <v>10</v>
@@ -4203,13 +4215,13 @@
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A258" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B258" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C258">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="D258">
         <v>11.5</v>
@@ -4217,13 +4229,13 @@
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A259" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B259" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C259">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="D259">
         <v>13</v>
@@ -4231,13 +4243,13 @@
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A260" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B260" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C260">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="D260">
         <v>15</v>
@@ -4245,511 +4257,511 @@
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A261" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B261" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C261">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="D261">
-        <v>7</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A262" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B262" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C262">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="D262">
-        <v>8.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A263" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B263" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C263">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="D263">
-        <v>10</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A264" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B264" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C264">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="D264">
-        <v>11.5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A265" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B265" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C265">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="D265">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A266" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B266" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C266">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="D266">
-        <v>15</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A267" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B267" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C267">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D267">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A268" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B268" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C268">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D268">
-        <v>8.5</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A269" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B269" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C269">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D269">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A270" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B270" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C270">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D270">
-        <v>11.5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A271" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B271" t="s">
         <v>47</v>
       </c>
       <c r="C271">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D271">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A272" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B272" t="s">
         <v>47</v>
       </c>
       <c r="C272">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D272">
-        <v>15</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A273" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B273" t="s">
         <v>47</v>
       </c>
       <c r="C273">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D273">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A274" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B274" t="s">
         <v>47</v>
       </c>
       <c r="C274">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D274">
-        <v>8.5</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A275" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B275" t="s">
         <v>47</v>
       </c>
       <c r="C275">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D275">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A276" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B276" t="s">
         <v>47</v>
       </c>
       <c r="C276">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="D276">
-        <v>11.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A277" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B277" t="s">
         <v>47</v>
       </c>
       <c r="C277">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="D277">
-        <v>13</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A278" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B278" t="s">
         <v>47</v>
       </c>
       <c r="C278">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="D278">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A279" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B279" t="s">
         <v>47</v>
       </c>
       <c r="C279">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="D279">
-        <v>7</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A280" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B280" t="s">
         <v>47</v>
       </c>
       <c r="C280">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="D280">
-        <v>8.5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A281" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B281" t="s">
         <v>47</v>
       </c>
       <c r="C281">
+        <v>5</v>
+      </c>
+      <c r="D281">
         <v>7</v>
-      </c>
-      <c r="D281">
-        <v>10</v>
       </c>
     </row>
     <row r="282" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A282" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B282" t="s">
         <v>47</v>
       </c>
       <c r="C282">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D282">
-        <v>11.5</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A283" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B283" t="s">
         <v>47</v>
       </c>
       <c r="C283">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D283">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A284" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B284" t="s">
         <v>47</v>
       </c>
       <c r="C284">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D284">
-        <v>15</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A285" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B285" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C285">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D285">
-        <v>8.5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A286" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B286" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C286">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D286">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A287" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B287" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C287">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D287">
-        <v>11.5</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A288" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B288" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C288">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D288">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A289" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B289" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C289">
-        <v>2.5</v>
+        <v>6</v>
       </c>
       <c r="D289">
-        <v>8.5</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A290" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B290" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C290">
-        <v>2.5</v>
+        <v>6</v>
       </c>
       <c r="D290">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A291" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B291" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C291">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="D291">
-        <v>11.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A292" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B292" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C292">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="D292">
-        <v>13</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A293" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B293" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C293">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D293">
-        <v>8.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="294" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A294" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B294" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C294">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D294">
-        <v>10</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A295" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B295" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C295">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D295">
-        <v>11.5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="296" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A296" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B296" t="s">
         <v>46</v>
       </c>
       <c r="C296">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="D296">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A297" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B297" t="s">
         <v>46</v>
@@ -4763,7 +4775,7 @@
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A298" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B298" t="s">
         <v>46</v>
@@ -4777,7 +4789,7 @@
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A299" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B299" t="s">
         <v>46</v>
@@ -4791,7 +4803,7 @@
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A300" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B300" t="s">
         <v>46</v>
@@ -4805,27 +4817,27 @@
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A301" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B301" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C301">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="D301">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="302" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A302" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B302" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C302">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="D302">
         <v>7</v>
@@ -4833,13 +4845,13 @@
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A303" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B303" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C303">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="D303">
         <v>8.5</v>
@@ -4847,13 +4859,13 @@
     </row>
     <row r="304" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A304" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B304" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C304">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="D304">
         <v>10</v>
@@ -4861,13 +4873,13 @@
     </row>
     <row r="305" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A305" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B305" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C305">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="D305">
         <v>11.5</v>
@@ -4875,13 +4887,13 @@
     </row>
     <row r="306" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A306" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B306" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C306">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="D306">
         <v>13</v>
@@ -4889,13 +4901,13 @@
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A307" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B307" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C307">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="D307">
         <v>15</v>
@@ -4903,909 +4915,909 @@
     </row>
     <row r="308" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A308" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B308" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C308">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D308">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="309" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A309" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B309" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C309">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D309">
-        <v>7</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="310" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A310" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B310" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C310">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D310">
-        <v>8.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="311" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A311" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B311" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C311">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D311">
-        <v>10</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="312" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A312" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B312" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C312">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D312">
-        <v>11.5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A313" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B313" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C313">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D313">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="314" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A314" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B314" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C314">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="D314">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="315" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A315" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B315" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C315">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D315">
-        <v>6</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A316" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B316" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C316">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D316">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="317" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A317" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B317" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C317">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D317">
-        <v>8.5</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="318" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A318" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B318" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C318">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D318">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="319" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A319" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B319" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C319">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D319">
-        <v>11.5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="320" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A320" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B320" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C320">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D320">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="321" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A321" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B321" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C321">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D321">
-        <v>15</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="322" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A322" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B322" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C322">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="D322">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="323" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A323" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B323" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C323">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="D323">
-        <v>7</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="324" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A324" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B324" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C324">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="D324">
-        <v>8.5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="325" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A325" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B325" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C325">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="D325">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="326" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A326" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B326" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C326">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="D326">
-        <v>11.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="327" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A327" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B327" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C327">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="D327">
-        <v>13</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="328" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A328" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B328" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C328">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="D328">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="329" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A329" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B329" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C329">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D329">
-        <v>6</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="330" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A330" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B330" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C330">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D330">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="331" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A331" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B331" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C331">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D331">
-        <v>8.5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="332" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A332" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B332" t="s">
         <v>45</v>
       </c>
       <c r="C332">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D332">
-        <v>10</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="333" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A333" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B333" t="s">
         <v>45</v>
       </c>
       <c r="C333">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D333">
-        <v>11.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="334" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A334" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B334" t="s">
         <v>45</v>
       </c>
       <c r="C334">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D334">
-        <v>13</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="335" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A335" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B335" t="s">
         <v>45</v>
       </c>
       <c r="C335">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D335">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="336" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A336" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B336" t="s">
         <v>45</v>
       </c>
       <c r="C336">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="D336">
-        <v>6</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="337" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A337" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B337" t="s">
         <v>45</v>
       </c>
       <c r="C337">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="D337">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="338" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A338" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B338" t="s">
         <v>45</v>
       </c>
       <c r="C338">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="D338">
-        <v>8.5</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="339" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A339" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B339" t="s">
         <v>45</v>
       </c>
       <c r="C339">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="D339">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="340" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A340" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B340" t="s">
         <v>45</v>
       </c>
       <c r="C340">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D340">
-        <v>11.5</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="341" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A341" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B341" t="s">
         <v>45</v>
       </c>
       <c r="C341">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D341">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="342" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A342" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B342" t="s">
         <v>45</v>
       </c>
       <c r="C342">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D342">
-        <v>15</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="343" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A343" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B343" t="s">
         <v>45</v>
       </c>
       <c r="C343">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D343">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="344" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A344" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B344" t="s">
         <v>45</v>
       </c>
       <c r="C344">
-        <v>7</v>
+        <v>3.5</v>
       </c>
       <c r="D344">
-        <v>7</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="345" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A345" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B345" t="s">
         <v>45</v>
       </c>
       <c r="C345">
-        <v>7</v>
+        <v>3.5</v>
       </c>
       <c r="D345">
-        <v>8.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="346" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A346" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B346" t="s">
         <v>45</v>
       </c>
       <c r="C346">
-        <v>7</v>
+        <v>3.5</v>
       </c>
       <c r="D346">
-        <v>10</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="347" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A347" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B347" t="s">
         <v>45</v>
       </c>
       <c r="C347">
-        <v>7</v>
+        <v>3.5</v>
       </c>
       <c r="D347">
-        <v>11.5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="348" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A348" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B348" t="s">
         <v>44</v>
       </c>
-      <c r="B348" t="s">
-        <v>45</v>
-      </c>
       <c r="C348">
-        <v>7</v>
+        <v>3.2</v>
       </c>
       <c r="D348">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="349" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A349" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B349" t="s">
         <v>44</v>
       </c>
-      <c r="B349" t="s">
-        <v>45</v>
-      </c>
       <c r="C349">
+        <v>3.2</v>
+      </c>
+      <c r="D349">
         <v>7</v>
-      </c>
-      <c r="D349">
-        <v>15</v>
       </c>
     </row>
     <row r="350" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A350" s="2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B350" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="C350">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="D350">
-        <v>8</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="351" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A351" t="s">
-        <v>51</v>
+      <c r="A351" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="B351" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="C351">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="D351">
         <v>10</v>
       </c>
     </row>
     <row r="352" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A352" t="s">
-        <v>51</v>
+      <c r="A352" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="B352" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="C352">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="D352">
-        <v>12</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="353" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A353" s="2" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="B353" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C353">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="D353">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="354" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A354" s="2" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="B354" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C354">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="D354">
-        <v>11.5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="355" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A355" s="2" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="B355" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C355">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="D355">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="356" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A356" s="2" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="B356" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C356">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="D356">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="357" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A357" s="2" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="B357" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C357">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="D357">
-        <v>10</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="358" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A358" s="2" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="B358" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C358">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="D358">
-        <v>11.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="359" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A359" s="2" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="B359" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C359">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="D359">
-        <v>13</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="360" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A360" s="2" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="B360" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C360">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="D360">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="361" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A361" s="2" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="B361" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C361">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="D361">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="362" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A362" s="2" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="B362" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C362">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="D362">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="363" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A363" s="2" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="B363" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C363">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="D363">
-        <v>11.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="364" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A364" s="2" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="B364" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C364">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="D364">
-        <v>13</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="365" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A365" s="2" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="B365" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C365">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="D365">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="366" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A366" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B366" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C366" s="2">
-        <v>5</v>
-      </c>
-      <c r="D366" s="2">
-        <v>8</v>
+        <v>43</v>
+      </c>
+      <c r="B366" t="s">
+        <v>44</v>
+      </c>
+      <c r="C366">
+        <v>4</v>
+      </c>
+      <c r="D366">
+        <v>11.5</v>
       </c>
     </row>
     <row r="367" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A367" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B367" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C367" s="2">
-        <v>5</v>
-      </c>
-      <c r="D367" s="2">
-        <v>10</v>
+        <v>43</v>
+      </c>
+      <c r="B367" t="s">
+        <v>44</v>
+      </c>
+      <c r="C367">
+        <v>4</v>
+      </c>
+      <c r="D367">
+        <v>13</v>
       </c>
     </row>
     <row r="368" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A368" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B368" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C368" s="2">
-        <v>5</v>
-      </c>
-      <c r="D368" s="2">
-        <v>11.5</v>
+        <v>43</v>
+      </c>
+      <c r="B368" t="s">
+        <v>44</v>
+      </c>
+      <c r="C368">
+        <v>4</v>
+      </c>
+      <c r="D368">
+        <v>15</v>
       </c>
     </row>
     <row r="369" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A369" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B369" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C369" s="2">
-        <v>5</v>
-      </c>
-      <c r="D369" s="2">
-        <v>13</v>
+        <v>43</v>
+      </c>
+      <c r="B369" t="s">
+        <v>44</v>
+      </c>
+      <c r="C369">
+        <v>4.5</v>
+      </c>
+      <c r="D369">
+        <v>6</v>
       </c>
     </row>
     <row r="370" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A370" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B370" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C370" s="2">
-        <v>5</v>
-      </c>
-      <c r="D370" s="2">
-        <v>16</v>
+        <v>43</v>
+      </c>
+      <c r="B370" t="s">
+        <v>44</v>
+      </c>
+      <c r="C370">
+        <v>4.5</v>
+      </c>
+      <c r="D370">
+        <v>7</v>
       </c>
     </row>
     <row r="371" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A371" s="2" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="B371" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="C371">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="D371">
-        <v>8</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="372" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A372" s="2" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="B372" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="C372">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="D372">
         <v>10</v>
@@ -5813,363 +5825,363 @@
     </row>
     <row r="373" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A373" s="2" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="B373" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="C373">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="D373">
-        <v>13</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="374" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A374" s="2" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="B374" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="C374">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D374">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="375" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A375" s="2" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="B375" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="C375">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="D375">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="376" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A376" s="2" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="B376" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="C376">
         <v>5</v>
       </c>
       <c r="D376">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="377" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A377" t="s">
-        <v>58</v>
+      <c r="A377" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="B377" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="C377">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="D377">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="378" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A378" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B378" t="s">
+        <v>44</v>
+      </c>
+      <c r="C378">
+        <v>5</v>
+      </c>
+      <c r="D378">
         <v>8.5</v>
       </c>
     </row>
-    <row r="378" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A378" t="s">
-        <v>58</v>
-      </c>
-      <c r="B378" t="s">
-        <v>57</v>
-      </c>
-      <c r="C378">
-        <v>3.5</v>
-      </c>
-      <c r="D378">
+    <row r="379" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A379" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B379" t="s">
+        <v>44</v>
+      </c>
+      <c r="C379">
+        <v>5</v>
+      </c>
+      <c r="D379">
         <v>10</v>
       </c>
     </row>
-    <row r="379" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A379" t="s">
-        <v>58</v>
-      </c>
-      <c r="B379" t="s">
-        <v>57</v>
-      </c>
-      <c r="C379">
-        <v>3.5</v>
-      </c>
-      <c r="D379">
+    <row r="380" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A380" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B380" t="s">
+        <v>44</v>
+      </c>
+      <c r="C380">
+        <v>5</v>
+      </c>
+      <c r="D380">
         <v>11.5</v>
       </c>
     </row>
-    <row r="380" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A380" t="s">
-        <v>58</v>
-      </c>
-      <c r="B380" t="s">
-        <v>57</v>
-      </c>
-      <c r="C380">
-        <v>3.5</v>
-      </c>
-      <c r="D380">
-        <v>13</v>
-      </c>
-    </row>
     <row r="381" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A381" t="s">
-        <v>58</v>
+      <c r="A381" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="B381" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="C381">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D381">
-        <v>7.3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="382" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A382" t="s">
-        <v>58</v>
+      <c r="A382" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="B382" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="C382">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D382">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="383" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A383" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B383" t="s">
+        <v>44</v>
+      </c>
+      <c r="C383">
+        <v>6</v>
+      </c>
+      <c r="D383">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="384" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A384" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B384" t="s">
+        <v>44</v>
+      </c>
+      <c r="C384">
+        <v>6</v>
+      </c>
+      <c r="D384">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="385" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A385" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B385" t="s">
+        <v>44</v>
+      </c>
+      <c r="C385">
+        <v>6</v>
+      </c>
+      <c r="D385">
         <v>8.5</v>
       </c>
     </row>
-    <row r="383" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A383" t="s">
-        <v>58</v>
-      </c>
-      <c r="B383" t="s">
-        <v>57</v>
-      </c>
-      <c r="C383">
-        <v>4</v>
-      </c>
-      <c r="D383">
+    <row r="386" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A386" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B386" t="s">
+        <v>44</v>
+      </c>
+      <c r="C386">
+        <v>6</v>
+      </c>
+      <c r="D386">
         <v>10</v>
       </c>
     </row>
-    <row r="384" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A384" t="s">
-        <v>58</v>
-      </c>
-      <c r="B384" t="s">
-        <v>57</v>
-      </c>
-      <c r="C384">
-        <v>4</v>
-      </c>
-      <c r="D384">
+    <row r="387" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A387" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B387" t="s">
+        <v>44</v>
+      </c>
+      <c r="C387">
+        <v>6</v>
+      </c>
+      <c r="D387">
         <v>11.5</v>
       </c>
     </row>
-    <row r="385" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A385" t="s">
-        <v>58</v>
-      </c>
-      <c r="B385" t="s">
-        <v>57</v>
-      </c>
-      <c r="C385">
-        <v>4</v>
-      </c>
-      <c r="D385">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="386" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A386" t="s">
-        <v>58</v>
-      </c>
-      <c r="B386" t="s">
-        <v>57</v>
-      </c>
-      <c r="C386">
-        <v>4.5</v>
-      </c>
-      <c r="D386">
-        <v>7.3</v>
-      </c>
-    </row>
-    <row r="387" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A387" t="s">
-        <v>58</v>
-      </c>
-      <c r="B387" t="s">
-        <v>57</v>
-      </c>
-      <c r="C387">
-        <v>4.5</v>
-      </c>
-      <c r="D387">
-        <v>8.5</v>
-      </c>
-    </row>
     <row r="388" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A388" t="s">
-        <v>58</v>
+      <c r="A388" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="B388" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="C388">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="D388">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="389" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A389" t="s">
-        <v>58</v>
+      <c r="A389" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="B389" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="C389">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="D389">
-        <v>11.5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="390" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A390" t="s">
-        <v>58</v>
+      <c r="A390" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="B390" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="C390">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="D390">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="391" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A391" t="s">
-        <v>58</v>
+      <c r="A391" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="B391" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="C391">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D391">
-        <v>7.3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="392" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A392" t="s">
-        <v>58</v>
+      <c r="A392" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="B392" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="C392">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D392">
         <v>8.5</v>
       </c>
     </row>
     <row r="393" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A393" t="s">
-        <v>58</v>
+      <c r="A393" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="B393" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="C393">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D393">
         <v>10</v>
       </c>
     </row>
     <row r="394" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A394" t="s">
-        <v>58</v>
+      <c r="A394" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="B394" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="C394">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D394">
         <v>11.5</v>
       </c>
     </row>
     <row r="395" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A395" t="s">
-        <v>58</v>
+      <c r="A395" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="B395" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="C395">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D395">
         <v>13</v>
       </c>
     </row>
     <row r="396" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A396" t="s">
-        <v>58</v>
+      <c r="A396" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="B396" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="C396">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="D396">
-        <v>7.3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="397" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A397" t="s">
-        <v>58</v>
+      <c r="A397" s="2" t="s">
+        <v>50</v>
       </c>
       <c r="B397" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="C397">
-        <v>5.5</v>
+        <v>3.6</v>
       </c>
       <c r="D397">
-        <v>8.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="398" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A398" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="B398" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="C398">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="D398">
         <v>10</v>
@@ -6177,575 +6189,1233 @@
     </row>
     <row r="399" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A399" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="B399" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="C399">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="D399">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="400" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A400" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B400" t="s">
+        <v>60</v>
+      </c>
+      <c r="C400">
+        <v>3.3</v>
+      </c>
+      <c r="D400">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="401" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A401" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B401" t="s">
+        <v>60</v>
+      </c>
+      <c r="C401">
+        <v>3.3</v>
+      </c>
+      <c r="D401">
         <v>11.5</v>
       </c>
     </row>
-    <row r="400" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A400" t="s">
-        <v>58</v>
-      </c>
-      <c r="B400" t="s">
-        <v>57</v>
-      </c>
-      <c r="C400">
-        <v>5.5</v>
-      </c>
-      <c r="D400">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="401" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A401" t="s">
-        <v>58</v>
-      </c>
-      <c r="B401" t="s">
-        <v>57</v>
-      </c>
-      <c r="C401">
-        <v>6</v>
-      </c>
-      <c r="D401">
-        <v>7.3</v>
-      </c>
-    </row>
     <row r="402" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A402" t="s">
-        <v>58</v>
+      <c r="A402" s="2" t="s">
+        <v>51</v>
       </c>
       <c r="B402" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C402">
-        <v>6</v>
+        <v>3.3</v>
       </c>
       <c r="D402">
-        <v>8.5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="403" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A403" t="s">
-        <v>58</v>
+      <c r="A403" s="2" t="s">
+        <v>51</v>
       </c>
       <c r="B403" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C403">
-        <v>6</v>
+        <v>3.3</v>
       </c>
       <c r="D403">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="404" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A404" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B404" t="s">
+        <v>60</v>
+      </c>
+      <c r="C404">
+        <v>3.75</v>
+      </c>
+      <c r="D404">
         <v>10</v>
       </c>
     </row>
-    <row r="404" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A404" t="s">
-        <v>58</v>
-      </c>
-      <c r="B404" t="s">
-        <v>57</v>
-      </c>
-      <c r="C404">
-        <v>6</v>
-      </c>
-      <c r="D404">
+    <row r="405" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A405" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B405" t="s">
+        <v>60</v>
+      </c>
+      <c r="C405">
+        <v>3.75</v>
+      </c>
+      <c r="D405">
         <v>11.5</v>
       </c>
     </row>
-    <row r="405" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A405" t="s">
-        <v>58</v>
-      </c>
-      <c r="B405" t="s">
-        <v>57</v>
-      </c>
-      <c r="C405">
-        <v>6</v>
-      </c>
-      <c r="D405">
-        <v>13</v>
-      </c>
-    </row>
     <row r="406" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A406" t="s">
-        <v>58</v>
+      <c r="A406" s="2" t="s">
+        <v>51</v>
       </c>
       <c r="B406" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C406">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="D406">
-        <v>8.5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="407" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A407" t="s">
-        <v>58</v>
+      <c r="A407" s="2" t="s">
+        <v>51</v>
       </c>
       <c r="B407" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C407">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="D407">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="408" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A408" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B408" t="s">
+        <v>60</v>
+      </c>
+      <c r="C408">
+        <v>4.2</v>
+      </c>
+      <c r="D408">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="409" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A409" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B409" t="s">
+        <v>60</v>
+      </c>
+      <c r="C409">
+        <v>4.2</v>
+      </c>
+      <c r="D409">
         <v>10</v>
       </c>
     </row>
-    <row r="408" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A408" t="s">
-        <v>58</v>
-      </c>
-      <c r="B408" t="s">
-        <v>61</v>
-      </c>
-      <c r="C408">
-        <v>3.5</v>
-      </c>
-      <c r="D408">
-        <v>11.5</v>
-      </c>
-    </row>
-    <row r="409" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A409" t="s">
-        <v>58</v>
-      </c>
-      <c r="B409" t="s">
-        <v>61</v>
-      </c>
-      <c r="C409">
-        <v>3.5</v>
-      </c>
-      <c r="D409">
-        <v>13</v>
-      </c>
-    </row>
     <row r="410" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A410" t="s">
-        <v>58</v>
+      <c r="A410" s="2" t="s">
+        <v>51</v>
       </c>
       <c r="B410" t="s">
         <v>60</v>
       </c>
       <c r="C410">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="D410">
-        <v>7</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="411" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A411" t="s">
-        <v>58</v>
+      <c r="A411" s="2" t="s">
+        <v>51</v>
       </c>
       <c r="B411" t="s">
         <v>60</v>
       </c>
       <c r="C411">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="D411">
-        <v>8.5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="412" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A412" t="s">
-        <v>58</v>
+      <c r="A412" s="2" t="s">
+        <v>51</v>
       </c>
       <c r="B412" t="s">
         <v>60</v>
       </c>
       <c r="C412">
+        <v>4.2</v>
+      </c>
+      <c r="D412">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="413" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A413" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B413" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C413" s="2">
+        <v>5</v>
+      </c>
+      <c r="D413" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="414" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A414" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B414" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C414" s="2">
+        <v>5</v>
+      </c>
+      <c r="D414" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="415" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A415" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B415" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C415" s="2">
+        <v>5</v>
+      </c>
+      <c r="D415" s="2">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="416" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A416" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B416" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C416" s="2">
+        <v>5</v>
+      </c>
+      <c r="D416" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="417" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A417" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B417" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C417" s="2">
+        <v>5</v>
+      </c>
+      <c r="D417" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="418" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A418" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B418" t="s">
+        <v>64</v>
+      </c>
+      <c r="C418">
+        <v>3.75</v>
+      </c>
+      <c r="D418">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="419" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A419" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B419" t="s">
+        <v>64</v>
+      </c>
+      <c r="C419">
+        <v>3.75</v>
+      </c>
+      <c r="D419">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="420" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A420" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B420" t="s">
+        <v>65</v>
+      </c>
+      <c r="C420">
+        <v>5</v>
+      </c>
+      <c r="D420">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="421" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A421" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B421" t="s">
+        <v>54</v>
+      </c>
+      <c r="C421">
+        <v>3.5</v>
+      </c>
+      <c r="D421">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="422" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A422" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B422" t="s">
+        <v>54</v>
+      </c>
+      <c r="C422">
         <v>4</v>
-      </c>
-      <c r="D412">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="413" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A413" t="s">
-        <v>58</v>
-      </c>
-      <c r="B413" t="s">
-        <v>60</v>
-      </c>
-      <c r="C413">
-        <v>4</v>
-      </c>
-      <c r="D413">
-        <v>11.5</v>
-      </c>
-    </row>
-    <row r="414" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A414" t="s">
-        <v>58</v>
-      </c>
-      <c r="B414" t="s">
-        <v>60</v>
-      </c>
-      <c r="C414">
-        <v>4</v>
-      </c>
-      <c r="D414">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="415" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A415" t="s">
-        <v>58</v>
-      </c>
-      <c r="B415" t="s">
-        <v>60</v>
-      </c>
-      <c r="C415">
-        <v>4.5</v>
-      </c>
-      <c r="D415">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="416" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A416" t="s">
-        <v>58</v>
-      </c>
-      <c r="B416" t="s">
-        <v>60</v>
-      </c>
-      <c r="C416">
-        <v>4.5</v>
-      </c>
-      <c r="D416">
-        <v>8.5</v>
-      </c>
-    </row>
-    <row r="417" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A417" t="s">
-        <v>58</v>
-      </c>
-      <c r="B417" t="s">
-        <v>60</v>
-      </c>
-      <c r="C417">
-        <v>4.5</v>
-      </c>
-      <c r="D417">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="418" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A418" t="s">
-        <v>58</v>
-      </c>
-      <c r="B418" t="s">
-        <v>60</v>
-      </c>
-      <c r="C418">
-        <v>4.5</v>
-      </c>
-      <c r="D418">
-        <v>11.5</v>
-      </c>
-    </row>
-    <row r="419" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A419" t="s">
-        <v>58</v>
-      </c>
-      <c r="B419" t="s">
-        <v>60</v>
-      </c>
-      <c r="C419">
-        <v>4.5</v>
-      </c>
-      <c r="D419">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="420" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A420" t="s">
-        <v>58</v>
-      </c>
-      <c r="B420" t="s">
-        <v>60</v>
-      </c>
-      <c r="C420">
-        <v>5</v>
-      </c>
-      <c r="D420">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="421" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A421" t="s">
-        <v>58</v>
-      </c>
-      <c r="B421" t="s">
-        <v>60</v>
-      </c>
-      <c r="C421">
-        <v>5</v>
-      </c>
-      <c r="D421">
-        <v>8.5</v>
-      </c>
-    </row>
-    <row r="422" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A422" t="s">
-        <v>58</v>
-      </c>
-      <c r="B422" t="s">
-        <v>60</v>
-      </c>
-      <c r="C422">
-        <v>5</v>
       </c>
       <c r="D422">
         <v>10</v>
       </c>
     </row>
     <row r="423" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A423" t="s">
-        <v>58</v>
+      <c r="A423" s="2" t="s">
+        <v>53</v>
       </c>
       <c r="B423" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C423">
         <v>5</v>
       </c>
       <c r="D423">
-        <v>11.5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="424" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A424" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B424" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C424">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="D424">
-        <v>13</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="425" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A425" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B425" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C425">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="D425">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="426" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A426" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B426" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C426">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="D426">
-        <v>8.5</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="427" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A427" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B427" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C427">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="D427">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="428" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A428" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B428" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C428">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D428">
-        <v>11.5</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="429" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A429" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B429" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C429">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D429">
-        <v>13</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="430" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A430" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B430" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C430">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="D430">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="431" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A431" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B431" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C431">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="D431">
-        <v>8.5</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="432" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A432" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B432" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C432">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="D432">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="433" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A433" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B433" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C433">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="D433">
-        <v>11.5</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="434" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A434" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B434" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C434">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="D434">
-        <v>13</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="435" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A435" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B435" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C435">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="D435">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="436" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A436" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B436" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C436">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="D436">
-        <v>8.5</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="437" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A437" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B437" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C437">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="D437">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="438" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A438" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B438" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C438">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D438">
-        <v>11.5</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="439" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A439" t="s">
+        <v>56</v>
+      </c>
+      <c r="B439" t="s">
+        <v>55</v>
+      </c>
+      <c r="C439">
+        <v>5</v>
+      </c>
+      <c r="D439">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="440" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A440" t="s">
+        <v>56</v>
+      </c>
+      <c r="B440" t="s">
+        <v>55</v>
+      </c>
+      <c r="C440">
+        <v>5</v>
+      </c>
+      <c r="D440">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="441" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A441" t="s">
+        <v>56</v>
+      </c>
+      <c r="B441" t="s">
+        <v>55</v>
+      </c>
+      <c r="C441">
+        <v>5</v>
+      </c>
+      <c r="D441">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="442" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A442" t="s">
+        <v>56</v>
+      </c>
+      <c r="B442" t="s">
+        <v>55</v>
+      </c>
+      <c r="C442">
+        <v>5</v>
+      </c>
+      <c r="D442">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="443" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A443" t="s">
+        <v>56</v>
+      </c>
+      <c r="B443" t="s">
+        <v>55</v>
+      </c>
+      <c r="C443">
+        <v>5.5</v>
+      </c>
+      <c r="D443">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="444" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A444" t="s">
+        <v>56</v>
+      </c>
+      <c r="B444" t="s">
+        <v>55</v>
+      </c>
+      <c r="C444">
+        <v>5.5</v>
+      </c>
+      <c r="D444">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="445" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A445" t="s">
+        <v>56</v>
+      </c>
+      <c r="B445" t="s">
+        <v>55</v>
+      </c>
+      <c r="C445">
+        <v>5.5</v>
+      </c>
+      <c r="D445">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="446" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A446" t="s">
+        <v>56</v>
+      </c>
+      <c r="B446" t="s">
+        <v>55</v>
+      </c>
+      <c r="C446">
+        <v>5.5</v>
+      </c>
+      <c r="D446">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="447" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A447" t="s">
+        <v>56</v>
+      </c>
+      <c r="B447" t="s">
+        <v>55</v>
+      </c>
+      <c r="C447">
+        <v>5.5</v>
+      </c>
+      <c r="D447">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="448" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A448" t="s">
+        <v>56</v>
+      </c>
+      <c r="B448" t="s">
+        <v>55</v>
+      </c>
+      <c r="C448">
+        <v>6</v>
+      </c>
+      <c r="D448">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="449" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A449" t="s">
+        <v>56</v>
+      </c>
+      <c r="B449" t="s">
+        <v>55</v>
+      </c>
+      <c r="C449">
+        <v>6</v>
+      </c>
+      <c r="D449">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="450" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A450" t="s">
+        <v>56</v>
+      </c>
+      <c r="B450" t="s">
+        <v>55</v>
+      </c>
+      <c r="C450">
+        <v>6</v>
+      </c>
+      <c r="D450">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="451" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A451" t="s">
+        <v>56</v>
+      </c>
+      <c r="B451" t="s">
+        <v>55</v>
+      </c>
+      <c r="C451">
+        <v>6</v>
+      </c>
+      <c r="D451">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="452" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A452" t="s">
+        <v>56</v>
+      </c>
+      <c r="B452" t="s">
+        <v>55</v>
+      </c>
+      <c r="C452">
+        <v>6</v>
+      </c>
+      <c r="D452">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="453" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A453" t="s">
+        <v>56</v>
+      </c>
+      <c r="B453" t="s">
+        <v>59</v>
+      </c>
+      <c r="C453">
+        <v>3.5</v>
+      </c>
+      <c r="D453">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="454" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A454" t="s">
+        <v>56</v>
+      </c>
+      <c r="B454" t="s">
+        <v>59</v>
+      </c>
+      <c r="C454">
+        <v>3.5</v>
+      </c>
+      <c r="D454">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="455" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A455" t="s">
+        <v>56</v>
+      </c>
+      <c r="B455" t="s">
+        <v>59</v>
+      </c>
+      <c r="C455">
+        <v>3.5</v>
+      </c>
+      <c r="D455">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="456" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A456" t="s">
+        <v>56</v>
+      </c>
+      <c r="B456" t="s">
+        <v>59</v>
+      </c>
+      <c r="C456">
+        <v>3.5</v>
+      </c>
+      <c r="D456">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="457" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A457" t="s">
+        <v>56</v>
+      </c>
+      <c r="B457" t="s">
         <v>58</v>
       </c>
-      <c r="B439" t="s">
-        <v>59</v>
-      </c>
-      <c r="C439">
+      <c r="C457">
+        <v>4</v>
+      </c>
+      <c r="D457">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="458" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A458" t="s">
+        <v>56</v>
+      </c>
+      <c r="B458" t="s">
+        <v>58</v>
+      </c>
+      <c r="C458">
+        <v>4</v>
+      </c>
+      <c r="D458">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="459" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A459" t="s">
+        <v>56</v>
+      </c>
+      <c r="B459" t="s">
+        <v>58</v>
+      </c>
+      <c r="C459">
+        <v>4</v>
+      </c>
+      <c r="D459">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="460" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A460" t="s">
+        <v>56</v>
+      </c>
+      <c r="B460" t="s">
+        <v>58</v>
+      </c>
+      <c r="C460">
+        <v>4</v>
+      </c>
+      <c r="D460">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="461" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A461" t="s">
+        <v>56</v>
+      </c>
+      <c r="B461" t="s">
+        <v>58</v>
+      </c>
+      <c r="C461">
+        <v>4</v>
+      </c>
+      <c r="D461">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="462" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A462" t="s">
+        <v>56</v>
+      </c>
+      <c r="B462" t="s">
+        <v>58</v>
+      </c>
+      <c r="C462">
+        <v>4.5</v>
+      </c>
+      <c r="D462">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="463" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A463" t="s">
+        <v>56</v>
+      </c>
+      <c r="B463" t="s">
+        <v>58</v>
+      </c>
+      <c r="C463">
+        <v>4.5</v>
+      </c>
+      <c r="D463">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="464" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A464" t="s">
+        <v>56</v>
+      </c>
+      <c r="B464" t="s">
+        <v>58</v>
+      </c>
+      <c r="C464">
+        <v>4.5</v>
+      </c>
+      <c r="D464">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="465" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A465" t="s">
+        <v>56</v>
+      </c>
+      <c r="B465" t="s">
+        <v>58</v>
+      </c>
+      <c r="C465">
+        <v>4.5</v>
+      </c>
+      <c r="D465">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="466" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A466" t="s">
+        <v>56</v>
+      </c>
+      <c r="B466" t="s">
+        <v>58</v>
+      </c>
+      <c r="C466">
+        <v>4.5</v>
+      </c>
+      <c r="D466">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="467" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A467" t="s">
+        <v>56</v>
+      </c>
+      <c r="B467" t="s">
+        <v>58</v>
+      </c>
+      <c r="C467">
+        <v>5</v>
+      </c>
+      <c r="D467">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="468" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A468" t="s">
+        <v>56</v>
+      </c>
+      <c r="B468" t="s">
+        <v>58</v>
+      </c>
+      <c r="C468">
+        <v>5</v>
+      </c>
+      <c r="D468">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="469" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A469" t="s">
+        <v>56</v>
+      </c>
+      <c r="B469" t="s">
+        <v>58</v>
+      </c>
+      <c r="C469">
+        <v>5</v>
+      </c>
+      <c r="D469">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="470" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A470" t="s">
+        <v>56</v>
+      </c>
+      <c r="B470" t="s">
+        <v>58</v>
+      </c>
+      <c r="C470">
+        <v>5</v>
+      </c>
+      <c r="D470">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="471" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A471" t="s">
+        <v>56</v>
+      </c>
+      <c r="B471" t="s">
+        <v>58</v>
+      </c>
+      <c r="C471">
+        <v>5</v>
+      </c>
+      <c r="D471">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="472" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A472" t="s">
+        <v>56</v>
+      </c>
+      <c r="B472" t="s">
+        <v>57</v>
+      </c>
+      <c r="C472">
+        <v>5</v>
+      </c>
+      <c r="D472">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="473" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A473" t="s">
+        <v>56</v>
+      </c>
+      <c r="B473" t="s">
+        <v>57</v>
+      </c>
+      <c r="C473">
+        <v>5</v>
+      </c>
+      <c r="D473">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="474" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A474" t="s">
+        <v>56</v>
+      </c>
+      <c r="B474" t="s">
+        <v>57</v>
+      </c>
+      <c r="C474">
+        <v>5</v>
+      </c>
+      <c r="D474">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="475" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A475" t="s">
+        <v>56</v>
+      </c>
+      <c r="B475" t="s">
+        <v>57</v>
+      </c>
+      <c r="C475">
+        <v>5</v>
+      </c>
+      <c r="D475">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="476" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A476" t="s">
+        <v>56</v>
+      </c>
+      <c r="B476" t="s">
+        <v>57</v>
+      </c>
+      <c r="C476">
+        <v>5</v>
+      </c>
+      <c r="D476">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="477" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A477" t="s">
+        <v>56</v>
+      </c>
+      <c r="B477" t="s">
+        <v>57</v>
+      </c>
+      <c r="C477">
+        <v>5.5</v>
+      </c>
+      <c r="D477">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="478" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A478" t="s">
+        <v>56</v>
+      </c>
+      <c r="B478" t="s">
+        <v>57</v>
+      </c>
+      <c r="C478">
+        <v>5.5</v>
+      </c>
+      <c r="D478">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="479" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A479" t="s">
+        <v>56</v>
+      </c>
+      <c r="B479" t="s">
+        <v>57</v>
+      </c>
+      <c r="C479">
+        <v>5.5</v>
+      </c>
+      <c r="D479">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="480" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A480" t="s">
+        <v>56</v>
+      </c>
+      <c r="B480" t="s">
+        <v>57</v>
+      </c>
+      <c r="C480">
+        <v>5.5</v>
+      </c>
+      <c r="D480">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="481" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A481" t="s">
+        <v>56</v>
+      </c>
+      <c r="B481" t="s">
+        <v>57</v>
+      </c>
+      <c r="C481">
+        <v>5.5</v>
+      </c>
+      <c r="D481">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="482" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A482" t="s">
+        <v>56</v>
+      </c>
+      <c r="B482" t="s">
+        <v>57</v>
+      </c>
+      <c r="C482">
         <v>6</v>
       </c>
-      <c r="D439">
+      <c r="D482">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="483" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A483" t="s">
+        <v>56</v>
+      </c>
+      <c r="B483" t="s">
+        <v>57</v>
+      </c>
+      <c r="C483">
+        <v>6</v>
+      </c>
+      <c r="D483">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="484" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A484" t="s">
+        <v>56</v>
+      </c>
+      <c r="B484" t="s">
+        <v>57</v>
+      </c>
+      <c r="C484">
+        <v>6</v>
+      </c>
+      <c r="D484">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="485" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A485" t="s">
+        <v>56</v>
+      </c>
+      <c r="B485" t="s">
+        <v>57</v>
+      </c>
+      <c r="C485">
+        <v>6</v>
+      </c>
+      <c r="D485">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="486" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A486" t="s">
+        <v>56</v>
+      </c>
+      <c r="B486" t="s">
+        <v>57</v>
+      </c>
+      <c r="C486">
+        <v>6</v>
+      </c>
+      <c r="D486">
         <v>13</v>
       </c>
     </row>
